--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2021/NORTH_CAROLINA_2021.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2021/NORTH_CAROLINA_2021.xlsx
@@ -859,7 +859,7 @@
         <v>24</v>
       </c>
       <c r="D28">
-        <v>0.0009764433052605883</v>
+        <v>0.0009764433052605884</v>
       </c>
     </row>
     <row r="29">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C189">
@@ -5971,7 +5971,7 @@
         <v>24</v>
       </c>
       <c r="D312">
-        <v>0.0009764433052605883</v>
+        <v>0.0009764433052605884</v>
       </c>
     </row>
     <row r="313">
@@ -6000,7 +6000,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C314">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C324">
@@ -7123,7 +7123,7 @@
         <v>24</v>
       </c>
       <c r="D376">
-        <v>0.0009764433052605883</v>
+        <v>0.0009764433052605884</v>
       </c>
     </row>
     <row r="377">
@@ -11137,7 +11137,7 @@
         <v>24</v>
       </c>
       <c r="D599">
-        <v>0.0009764433052605883</v>
+        <v>0.0009764433052605884</v>
       </c>
     </row>
     <row r="600">
@@ -11983,7 +11983,7 @@
         <v>24</v>
       </c>
       <c r="D646">
-        <v>0.0009764433052605883</v>
+        <v>0.0009764433052605884</v>
       </c>
     </row>
     <row r="647">
@@ -12919,7 +12919,7 @@
         <v>24</v>
       </c>
       <c r="D698">
-        <v>0.0009764433052605883</v>
+        <v>0.0009764433052605884</v>
       </c>
     </row>
     <row r="699">
@@ -16134,7 +16134,7 @@
       </c>
       <c r="B877" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C877">
@@ -16152,7 +16152,7 @@
       </c>
       <c r="B878" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C878">
@@ -17358,7 +17358,7 @@
       </c>
       <c r="B945" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C945">
@@ -17376,7 +17376,7 @@
       </c>
       <c r="B946" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 26 -</t>
+          <t>San Pedro Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C946">
@@ -17574,7 +17574,7 @@
       </c>
       <c r="B957" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C957">
@@ -20047,7 +20047,7 @@
         <v>24</v>
       </c>
       <c r="D1094">
-        <v>0.0009764433052605883</v>
+        <v>0.0009764433052605884</v>
       </c>
     </row>
     <row r="1095">
